--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\ProjectM\MYBharat-Automation\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44C7E934-D522-4E4D-A5A8-FFF584595F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F1AB7D-46BF-4150-9D59-970E642442BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AF48352-515E-4DC0-AA5C-BFF759C0F978}"/>
+    <workbookView xWindow="6552" yWindow="5232" windowWidth="17280" windowHeight="8880" xr2:uid="{9AF48352-515E-4DC0-AA5C-BFF759C0F978}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Mega_Event_Name</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Automation Mega Event 1528</t>
+  </si>
+  <si>
+    <t>Automation Mega Event 3888</t>
   </si>
 </sst>
 </file>
@@ -432,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A22B34-7537-40DA-B43C-DE3D9D0AA4E0}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="16.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -443,39 +446,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s" s="0">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s" s="0">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Mega_Event_Name</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Automation Mega Event 3888</t>
+  </si>
+  <si>
+    <t>Seva Se Seekhen</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A22B34-7537-40DA-B43C-DE3D9D0AA4E0}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
@@ -486,6 +489,16 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Mega_Event_Name</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Seva Se Seekhen</t>
+  </si>
+  <si>
+    <t>Seeva See Seekhen</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A22B34-7537-40DA-B43C-DE3D9D0AA4E0}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
@@ -499,6 +502,21 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -1,72 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\ProjectM\MYBharat-Automation\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F1AB7D-46BF-4150-9D59-970E642442BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="6552" yWindow="5232" windowWidth="17280" windowHeight="8880" xr2:uid="{9AF48352-515E-4DC0-AA5C-BFF759C0F978}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6552" yWindow="5232" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MegaEvents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
-  <si>
-    <t>Mega_Event_Name</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 9579</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 5017</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 6967</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 9809</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 6293</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 5530</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 1528</t>
-  </si>
-  <si>
-    <t>Automation Mega Event 3888</t>
-  </si>
-  <si>
-    <t>Seva Se Seekhen</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
   <si>
     <t>Seeva See Seekhen</t>
   </si>
@@ -74,20 +21,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -106,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,81 +446,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A22B34-7537-40DA-B43C-DE3D9D0AA4E0}">
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+    <row r="1">
+      <c r="A1" t="inlineStr" s="0">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="0">
+        <is>
+          <t>Mega_Event_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 9579</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 5017</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 6967</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 9809</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 6293</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 5530</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 1528</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t>Automation Mega Event 3888</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t>Seva Se Seekhen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t>Seva Se Seekhen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t>Seva Se Seekhen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t>Seva Se Seekhen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>Seeva See Seekhen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>10</v>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="1">
   <si>
     <t>Seeva See Seekhen</t>
   </si>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
@@ -572,6 +572,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Create_MegaEvent_Prod.xlsx
+++ b/resources/Create_MegaEvent_Prod.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="1">
   <si>
     <t>Seeva See Seekhen</t>
   </si>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.21875"/>
@@ -592,6 +592,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
